--- a/gstdatabase/REGISTRATION.xlsx
+++ b/gstdatabase/REGISTRATION.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://infosystechnologies-my.sharepoint.com/personal/sai_enjeti_ad_infosys_com/Documents/Documents/GST Statistics Downloads 31st Jul 26/GST Statistics Downloads 31st Jul 26/Downloads/Registration/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GSTN\Krishnan Sir\Monthly Report\Aug-26\GST Statistics Downloads 31st Aug 26\Downloads\Registration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{61065DE5-6E1C-4A06-A4DF-5BE4D49607A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EB75211-BDA8-493B-AAF9-8F78D7C0D0AB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEE93C08-A54F-433A-B67B-F7C42867BF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Registration" sheetId="2" r:id="rId1"/>
-    <sheet name="Gender based analysis" sheetId="3" r:id="rId2"/>
+    <sheet name="Gender Based Analysis" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Registration!$A$2:$L$41</definedName>
@@ -195,9 +195,6 @@
     <t>State Code</t>
   </si>
   <si>
-    <t>Gender based analysis</t>
-  </si>
-  <si>
     <t>Constitution of business</t>
   </si>
   <si>
@@ -344,7 +341,10 @@
     </r>
   </si>
   <si>
-    <t>State Wise Registration Typewise No. of Active Tax payers as on 31st Jul 26</t>
+    <t>State Wise Registration Typewise No. of Active Tax payers as on 31st Aug 26</t>
+  </si>
+  <si>
+    <t>Gender Based Analysis</t>
   </si>
 </sst>
 </file>
@@ -352,9 +352,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
@@ -713,7 +713,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -746,8 +746,8 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -756,21 +756,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -804,6 +801,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1087,39 +1087,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.6328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.6328125" style="3" customWidth="1"/>
-    <col min="3" max="5" width="16.453125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.90625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="11.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.6640625" style="3" customWidth="1"/>
+    <col min="3" max="5" width="16.44140625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" style="3" customWidth="1"/>
     <col min="7" max="7" width="18" style="3" customWidth="1"/>
-    <col min="8" max="8" width="17.6328125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="14.453125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="9.6328125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="13.453125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="16.453125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="15.36328125" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9.08984375" style="3"/>
+    <col min="8" max="8" width="17.6640625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="13.44140625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="16.44140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15.33203125" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="9.109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-    </row>
-    <row r="2" spans="1:12" ht="48.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+    </row>
+    <row r="2" spans="1:12" ht="48.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>50</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1165,10 +1165,10 @@
         <v>24</v>
       </c>
       <c r="C3" s="6">
-        <v>152446</v>
+        <v>155211</v>
       </c>
       <c r="D3" s="6">
-        <v>9183</v>
+        <v>9192</v>
       </c>
       <c r="E3" s="6">
         <v>30</v>
@@ -1177,10 +1177,10 @@
         <v>9</v>
       </c>
       <c r="G3" s="6">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H3" s="6">
-        <v>8424</v>
+        <v>8429</v>
       </c>
       <c r="I3" s="6">
         <v>0</v>
@@ -1193,10 +1193,10 @@
       </c>
       <c r="L3" s="6">
         <f>SUM(C3:J3)</f>
-        <v>170362</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>173143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1204,22 +1204,22 @@
         <v>23</v>
       </c>
       <c r="C4" s="6">
-        <v>119499</v>
+        <v>120746</v>
       </c>
       <c r="D4" s="6">
-        <v>15188</v>
+        <v>15150</v>
       </c>
       <c r="E4" s="6">
         <v>64</v>
       </c>
       <c r="F4" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="6">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H4" s="6">
-        <v>2533</v>
+        <v>2546</v>
       </c>
       <c r="I4" s="6">
         <v>0</v>
@@ -1232,10 +1232,10 @@
       </c>
       <c r="L4" s="6">
         <f t="shared" ref="L4:L41" si="0">SUM(C4:J4)</f>
-        <v>137624</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>138848</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1243,22 +1243,22 @@
         <v>38</v>
       </c>
       <c r="C5" s="6">
-        <v>405536</v>
+        <v>409896</v>
       </c>
       <c r="D5" s="6">
-        <v>35854</v>
+        <v>35899</v>
       </c>
       <c r="E5" s="6">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F5" s="6">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="G5" s="6">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H5" s="6">
-        <v>11077</v>
+        <v>11126</v>
       </c>
       <c r="I5" s="6">
         <v>0</v>
@@ -1271,10 +1271,10 @@
       </c>
       <c r="L5" s="6">
         <f t="shared" si="0"/>
-        <v>453594</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>458049</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1282,22 +1282,22 @@
         <v>15</v>
       </c>
       <c r="C6" s="6">
-        <v>30969</v>
+        <v>31242</v>
       </c>
       <c r="D6" s="6">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="E6" s="6">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F6" s="6">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="G6" s="6">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H6" s="6">
-        <v>956</v>
+        <v>959</v>
       </c>
       <c r="I6" s="6">
         <v>0</v>
@@ -1310,10 +1310,10 @@
       </c>
       <c r="L6" s="6">
         <f t="shared" si="0"/>
-        <v>34030</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>34333</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1321,25 +1321,25 @@
         <v>45</v>
       </c>
       <c r="C7" s="6">
-        <v>197647</v>
+        <v>200778</v>
       </c>
       <c r="D7" s="6">
-        <v>29401</v>
+        <v>29365</v>
       </c>
       <c r="E7" s="6">
         <v>92</v>
       </c>
       <c r="F7" s="6">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="G7" s="6">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H7" s="6">
-        <v>4658</v>
+        <v>5139</v>
       </c>
       <c r="I7" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2">
         <v>0</v>
@@ -1349,10 +1349,10 @@
       </c>
       <c r="L7" s="6">
         <f t="shared" si="0"/>
-        <v>232381</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>235970</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1360,38 +1360,38 @@
         <v>22</v>
       </c>
       <c r="C8" s="6">
-        <v>629112</v>
+        <v>637403</v>
       </c>
       <c r="D8" s="6">
-        <v>13661</v>
+        <v>13666</v>
       </c>
       <c r="E8" s="6">
-        <v>2705</v>
+        <v>2725</v>
       </c>
       <c r="F8" s="6">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G8" s="6">
-        <v>1393</v>
+        <v>1398</v>
       </c>
       <c r="H8" s="6">
-        <v>8463</v>
+        <v>8550</v>
       </c>
       <c r="I8" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J8" s="2">
         <v>0</v>
       </c>
       <c r="K8" s="6">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L8" s="6">
         <f t="shared" si="0"/>
-        <v>655358</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>663765</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1399,22 +1399,22 @@
         <v>19</v>
       </c>
       <c r="C9" s="6">
-        <v>900961</v>
+        <v>911705</v>
       </c>
       <c r="D9" s="6">
-        <v>15418</v>
+        <v>15352</v>
       </c>
       <c r="E9" s="6">
-        <v>3777</v>
+        <v>3778</v>
       </c>
       <c r="F9" s="6">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="G9" s="6">
-        <v>1998</v>
+        <v>2003</v>
       </c>
       <c r="H9" s="6">
-        <v>7931</v>
+        <v>8006</v>
       </c>
       <c r="I9" s="6">
         <v>7</v>
@@ -1423,14 +1423,14 @@
         <v>0</v>
       </c>
       <c r="K9" s="6">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L9" s="6">
         <f t="shared" si="0"/>
-        <v>930215</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>940957</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1438,22 +1438,22 @@
         <v>39</v>
       </c>
       <c r="C10" s="6">
-        <v>852027</v>
+        <v>851822</v>
       </c>
       <c r="D10" s="6">
-        <v>112035</v>
+        <v>109485</v>
       </c>
       <c r="E10" s="6">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="F10" s="6">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G10" s="6">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="H10" s="6">
-        <v>27720</v>
+        <v>27919</v>
       </c>
       <c r="I10" s="6">
         <v>0</v>
@@ -1466,10 +1466,10 @@
       </c>
       <c r="L10" s="6">
         <f t="shared" si="0"/>
-        <v>993412</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>990869</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1477,22 +1477,22 @@
         <v>44</v>
       </c>
       <c r="C11" s="6">
-        <v>1848771</v>
+        <v>1874990</v>
       </c>
       <c r="D11" s="6">
-        <v>283999</v>
+        <v>283633</v>
       </c>
       <c r="E11" s="6">
         <v>1484</v>
       </c>
       <c r="F11" s="6">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="G11" s="6">
-        <v>1914</v>
+        <v>1920</v>
       </c>
       <c r="H11" s="6">
-        <v>78016</v>
+        <v>78301</v>
       </c>
       <c r="I11" s="6">
         <v>1</v>
@@ -1501,14 +1501,14 @@
         <v>0</v>
       </c>
       <c r="K11" s="6">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="L11" s="6">
         <f t="shared" si="0"/>
-        <v>2214203</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>2240352</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1516,22 +1516,22 @@
         <v>13</v>
       </c>
       <c r="C12" s="6">
-        <v>630014</v>
+        <v>642163</v>
       </c>
       <c r="D12" s="6">
-        <v>78804</v>
+        <v>78414</v>
       </c>
       <c r="E12" s="6">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F12" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G12" s="6">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H12" s="6">
-        <v>19277</v>
+        <v>19356</v>
       </c>
       <c r="I12" s="6">
         <v>0</v>
@@ -1544,10 +1544,10 @@
       </c>
       <c r="L12" s="6">
         <f t="shared" si="0"/>
-        <v>728838</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>740674</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1555,10 +1555,10 @@
         <v>40</v>
       </c>
       <c r="C13" s="6">
-        <v>10572</v>
+        <v>10728</v>
       </c>
       <c r="D13" s="6">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E13" s="6">
         <v>4</v>
@@ -1567,10 +1567,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="6">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="H13" s="6">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="I13" s="6">
         <v>0</v>
@@ -1583,10 +1583,10 @@
       </c>
       <c r="L13" s="6">
         <f t="shared" si="0"/>
-        <v>11940</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>12099</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="6">
-        <v>19026</v>
+        <v>19397</v>
       </c>
       <c r="D14" s="6">
         <v>1833</v>
@@ -1606,10 +1606,10 @@
         <v>0</v>
       </c>
       <c r="G14" s="6">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H14" s="6">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="I14" s="6">
         <v>0</v>
@@ -1622,10 +1622,10 @@
       </c>
       <c r="L14" s="6">
         <f t="shared" si="0"/>
-        <v>22706</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>23080</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1633,19 +1633,19 @@
         <v>34</v>
       </c>
       <c r="C15" s="6">
-        <v>9413</v>
+        <v>9555</v>
       </c>
       <c r="D15" s="6">
-        <v>1730</v>
+        <v>1724</v>
       </c>
       <c r="E15" s="6">
         <v>3</v>
       </c>
       <c r="F15" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G15" s="6">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H15" s="6">
         <v>418</v>
@@ -1661,10 +1661,10 @@
       </c>
       <c r="L15" s="6">
         <f t="shared" si="0"/>
-        <v>11703</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>11843</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>31</v>
       </c>
       <c r="C16" s="6">
-        <v>14263</v>
+        <v>14299</v>
       </c>
       <c r="D16" s="6">
         <v>1363</v>
@@ -1684,10 +1684,10 @@
         <v>0</v>
       </c>
       <c r="G16" s="6">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="H16" s="6">
-        <v>728</v>
+        <v>733</v>
       </c>
       <c r="I16" s="6">
         <v>0</v>
@@ -1700,10 +1700,10 @@
       </c>
       <c r="L16" s="6">
         <f t="shared" si="0"/>
-        <v>16542</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>16585</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1711,22 +1711,22 @@
         <v>33</v>
       </c>
       <c r="C17" s="6">
-        <v>9359</v>
+        <v>9549</v>
       </c>
       <c r="D17" s="6">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E17" s="6">
         <v>4</v>
       </c>
       <c r="F17" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" s="6">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H17" s="6">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="I17" s="6">
         <v>0</v>
@@ -1739,10 +1739,10 @@
       </c>
       <c r="L17" s="6">
         <f t="shared" si="0"/>
-        <v>10075</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>10272</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1750,22 +1750,22 @@
         <v>43</v>
       </c>
       <c r="C18" s="6">
-        <v>32071</v>
+        <v>32490</v>
       </c>
       <c r="D18" s="6">
-        <v>2805</v>
+        <v>2806</v>
       </c>
       <c r="E18" s="6">
         <v>11</v>
       </c>
       <c r="F18" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="6">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H18" s="6">
-        <v>1452</v>
+        <v>1455</v>
       </c>
       <c r="I18" s="6">
         <v>0</v>
@@ -1778,10 +1778,10 @@
       </c>
       <c r="L18" s="6">
         <f t="shared" si="0"/>
-        <v>36523</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>36949</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -1789,10 +1789,10 @@
         <v>32</v>
       </c>
       <c r="C19" s="6">
-        <v>31455</v>
+        <v>32076</v>
       </c>
       <c r="D19" s="6">
-        <v>2017</v>
+        <v>2008</v>
       </c>
       <c r="E19" s="6">
         <v>14</v>
@@ -1801,10 +1801,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="6">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H19" s="6">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="I19" s="6">
         <v>0</v>
@@ -1817,10 +1817,10 @@
       </c>
       <c r="L19" s="6">
         <f t="shared" si="0"/>
-        <v>34465</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>35082</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -1828,22 +1828,22 @@
         <v>12</v>
       </c>
       <c r="C20" s="6">
-        <v>218664</v>
+        <v>223419</v>
       </c>
       <c r="D20" s="6">
-        <v>29920</v>
+        <v>29918</v>
       </c>
       <c r="E20" s="6">
         <v>77</v>
       </c>
       <c r="F20" s="6">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G20" s="6">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="H20" s="6">
-        <v>7846</v>
+        <v>8078</v>
       </c>
       <c r="I20" s="6">
         <v>0</v>
@@ -1852,14 +1852,14 @@
         <v>0</v>
       </c>
       <c r="K20" s="6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L20" s="6">
         <f t="shared" si="0"/>
-        <v>256975</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>261960</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -1867,22 +1867,22 @@
         <v>46</v>
       </c>
       <c r="C21" s="6">
-        <v>811072</v>
+        <v>824823</v>
       </c>
       <c r="D21" s="6">
-        <v>51383</v>
+        <v>51343</v>
       </c>
       <c r="E21" s="6">
         <v>1220</v>
       </c>
       <c r="F21" s="6">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="G21" s="6">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="H21" s="6">
-        <v>15900</v>
+        <v>15959</v>
       </c>
       <c r="I21" s="6">
         <v>3</v>
@@ -1891,14 +1891,14 @@
         <v>0</v>
       </c>
       <c r="K21" s="6">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L21" s="6">
         <f t="shared" si="0"/>
-        <v>880771</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>894572</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -1906,22 +1906,22 @@
         <v>25</v>
       </c>
       <c r="C22" s="6">
-        <v>223169</v>
+        <v>226400</v>
       </c>
       <c r="D22" s="6">
-        <v>13033</v>
+        <v>12966</v>
       </c>
       <c r="E22" s="6">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F22" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G22" s="6">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="H22" s="6">
-        <v>5198</v>
+        <v>5228</v>
       </c>
       <c r="I22" s="6">
         <v>0</v>
@@ -1930,14 +1930,14 @@
         <v>0</v>
       </c>
       <c r="K22" s="6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L22" s="6">
         <f t="shared" si="0"/>
-        <v>241923</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>245123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -1945,22 +1945,22 @@
         <v>35</v>
       </c>
       <c r="C23" s="6">
-        <v>356638</v>
+        <v>361284</v>
       </c>
       <c r="D23" s="6">
-        <v>24303</v>
+        <v>24203</v>
       </c>
       <c r="E23" s="6">
         <v>86</v>
       </c>
       <c r="F23" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="6">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="H23" s="6">
-        <v>5903</v>
+        <v>5970</v>
       </c>
       <c r="I23" s="6">
         <v>0</v>
@@ -1969,14 +1969,14 @@
         <v>0</v>
       </c>
       <c r="K23" s="6">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L23" s="6">
         <f t="shared" si="0"/>
-        <v>387386</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>392001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -1984,22 +1984,22 @@
         <v>16</v>
       </c>
       <c r="C24" s="6">
-        <v>163631</v>
+        <v>165691</v>
       </c>
       <c r="D24" s="6">
-        <v>29541</v>
+        <v>29808</v>
       </c>
       <c r="E24" s="6">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F24" s="6">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="G24" s="6">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H24" s="6">
-        <v>15102</v>
+        <v>15358</v>
       </c>
       <c r="I24" s="6">
         <v>0</v>
@@ -2012,10 +2012,10 @@
       </c>
       <c r="L24" s="6">
         <f t="shared" si="0"/>
-        <v>208881</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>211499</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -2023,22 +2023,22 @@
         <v>30</v>
       </c>
       <c r="C25" s="6">
-        <v>554370</v>
+        <v>561911</v>
       </c>
       <c r="D25" s="6">
-        <v>37884</v>
+        <v>37769</v>
       </c>
       <c r="E25" s="6">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F25" s="6">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="G25" s="6">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H25" s="6">
-        <v>27304</v>
+        <v>27359</v>
       </c>
       <c r="I25" s="6">
         <v>0</v>
@@ -2047,14 +2047,14 @@
         <v>0</v>
       </c>
       <c r="K25" s="6">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L25" s="6">
         <f t="shared" si="0"/>
-        <v>620858</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>628353</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -2062,38 +2062,38 @@
         <v>21</v>
       </c>
       <c r="C26" s="6">
-        <v>1312143</v>
+        <v>1328857</v>
       </c>
       <c r="D26" s="6">
-        <v>88821</v>
+        <v>89015</v>
       </c>
       <c r="E26" s="6">
-        <v>2028</v>
+        <v>2036</v>
       </c>
       <c r="F26" s="6">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G26" s="6">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="H26" s="6">
-        <v>38598</v>
+        <v>38903</v>
       </c>
       <c r="I26" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J26" s="2">
         <v>0</v>
       </c>
       <c r="K26" s="6">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="L26" s="6">
         <f t="shared" si="0"/>
-        <v>1442869</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1460099</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -2140,22 +2140,22 @@
         <v>17</v>
       </c>
       <c r="C28" s="6">
-        <v>15918</v>
+        <v>15978</v>
       </c>
       <c r="D28" s="6">
-        <v>563</v>
+        <v>544</v>
       </c>
       <c r="E28" s="6">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F28" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" s="6">
         <v>224</v>
       </c>
       <c r="H28" s="6">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="I28" s="6">
         <v>0</v>
@@ -2168,36 +2168,36 @@
       </c>
       <c r="L28" s="6">
         <f t="shared" si="0"/>
-        <v>17146</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>17190</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C29" s="6">
-        <v>1892625</v>
+        <v>1915643</v>
       </c>
       <c r="D29" s="6">
-        <v>116664</v>
+        <v>116801</v>
       </c>
       <c r="E29" s="6">
-        <v>7923</v>
+        <v>7944</v>
       </c>
       <c r="F29" s="6">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="G29" s="6">
-        <v>2036</v>
+        <v>2051</v>
       </c>
       <c r="H29" s="6">
-        <v>54642</v>
+        <v>54709</v>
       </c>
       <c r="I29" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J29" s="2">
         <v>0</v>
@@ -2207,10 +2207,10 @@
       </c>
       <c r="L29" s="6">
         <f t="shared" si="0"/>
-        <v>2074080</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>2097327</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2218,38 +2218,38 @@
         <v>26</v>
       </c>
       <c r="C30" s="6">
-        <v>1005922</v>
+        <v>1018081</v>
       </c>
       <c r="D30" s="6">
-        <v>96195</v>
+        <v>96227</v>
       </c>
       <c r="E30" s="6">
-        <v>2431</v>
+        <v>2449</v>
       </c>
       <c r="F30" s="6">
-        <v>156</v>
+        <v>199</v>
       </c>
       <c r="G30" s="6">
-        <v>1928</v>
+        <v>1945</v>
       </c>
       <c r="H30" s="6">
-        <v>24368</v>
+        <v>24457</v>
       </c>
       <c r="I30" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J30" s="2">
         <v>0</v>
       </c>
       <c r="K30" s="6">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L30" s="6">
         <f t="shared" si="0"/>
-        <v>1131004</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1143360</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2257,22 +2257,22 @@
         <v>20</v>
       </c>
       <c r="C31" s="6">
-        <v>44009</v>
+        <v>44587</v>
       </c>
       <c r="D31" s="6">
-        <v>5343</v>
+        <v>5352</v>
       </c>
       <c r="E31" s="6">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F31" s="6">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G31" s="6">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="H31" s="6">
-        <v>1019</v>
+        <v>1025</v>
       </c>
       <c r="I31" s="6">
         <v>0</v>
@@ -2285,10 +2285,10 @@
       </c>
       <c r="L31" s="6">
         <f t="shared" si="0"/>
-        <v>50861</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>51460</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2296,10 +2296,10 @@
         <v>29</v>
       </c>
       <c r="C32" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="D32" s="2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E32" s="2">
         <v>0</v>
@@ -2308,10 +2308,10 @@
         <v>0</v>
       </c>
       <c r="G32" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H32" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I32" s="2">
         <v>0</v>
@@ -2324,10 +2324,10 @@
       </c>
       <c r="L32" s="6">
         <f t="shared" si="0"/>
-        <v>541</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2335,25 +2335,25 @@
         <v>27</v>
       </c>
       <c r="C33" s="6">
-        <v>389392</v>
+        <v>393276</v>
       </c>
       <c r="D33" s="6">
-        <v>51398</v>
+        <v>51513</v>
       </c>
       <c r="E33" s="6">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="F33" s="6">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="G33" s="6">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="H33" s="6">
-        <v>10498</v>
+        <v>10525</v>
       </c>
       <c r="I33" s="6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J33" s="2">
         <v>0</v>
@@ -2363,10 +2363,10 @@
       </c>
       <c r="L33" s="6">
         <f t="shared" si="0"/>
-        <v>452855</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>456884</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2374,22 +2374,22 @@
         <v>41</v>
       </c>
       <c r="C34" s="6">
-        <v>1173931</v>
+        <v>1184493</v>
       </c>
       <c r="D34" s="6">
-        <v>62071</v>
+        <v>62054</v>
       </c>
       <c r="E34" s="6">
-        <v>1784</v>
+        <v>1792</v>
       </c>
       <c r="F34" s="6">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G34" s="6">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="H34" s="6">
-        <v>24599</v>
+        <v>24821</v>
       </c>
       <c r="I34" s="6">
         <v>2</v>
@@ -2398,14 +2398,14 @@
         <v>0</v>
       </c>
       <c r="K34" s="6">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L34" s="6">
         <f t="shared" si="0"/>
-        <v>1264150</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1274915</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2413,22 +2413,22 @@
         <v>37</v>
       </c>
       <c r="C35" s="6">
-        <v>23932</v>
+        <v>24079</v>
       </c>
       <c r="D35" s="6">
-        <v>2154</v>
+        <v>2134</v>
       </c>
       <c r="E35" s="6">
         <v>30</v>
       </c>
       <c r="F35" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G35" s="6">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H35" s="6">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="I35" s="6">
         <v>0</v>
@@ -2441,10 +2441,10 @@
       </c>
       <c r="L35" s="6">
         <f t="shared" si="0"/>
-        <v>26841</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>26974</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2452,10 +2452,10 @@
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>5696</v>
+        <v>5819</v>
       </c>
       <c r="D36" s="6">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="E36" s="6">
         <v>6</v>
@@ -2467,7 +2467,7 @@
         <v>129</v>
       </c>
       <c r="H36" s="6">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="I36" s="6">
         <v>0</v>
@@ -2480,10 +2480,10 @@
       </c>
       <c r="L36" s="6">
         <f t="shared" si="0"/>
-        <v>6941</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>7069</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2491,38 +2491,38 @@
         <v>42</v>
       </c>
       <c r="C37" s="6">
-        <v>515683</v>
+        <v>522582</v>
       </c>
       <c r="D37" s="6">
-        <v>46912</v>
+        <v>46781</v>
       </c>
       <c r="E37" s="6">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="F37" s="6">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="G37" s="6">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="H37" s="6">
-        <v>19731</v>
+        <v>19674</v>
       </c>
       <c r="I37" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J37" s="2">
         <v>0</v>
       </c>
       <c r="K37" s="6">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L37" s="6">
         <f t="shared" si="0"/>
-        <v>584202</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>590940</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2530,22 +2530,22 @@
         <v>10</v>
       </c>
       <c r="C38" s="6">
-        <v>372981</v>
+        <v>377870</v>
       </c>
       <c r="D38" s="6">
-        <v>80400</v>
+        <v>80320</v>
       </c>
       <c r="E38" s="6">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F38" s="6">
         <v>55</v>
       </c>
       <c r="G38" s="6">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="H38" s="6">
-        <v>7602</v>
+        <v>7780</v>
       </c>
       <c r="I38" s="6">
         <v>0</v>
@@ -2554,14 +2554,14 @@
         <v>0</v>
       </c>
       <c r="K38" s="6">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L38" s="6">
         <f t="shared" si="0"/>
-        <v>461920</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>466911</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2569,22 +2569,22 @@
         <v>28</v>
       </c>
       <c r="C39" s="6">
-        <v>9521</v>
+        <v>9643</v>
       </c>
       <c r="D39" s="6">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="E39" s="6">
         <v>1</v>
       </c>
       <c r="F39" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G39" s="6">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H39" s="6">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="I39" s="6">
         <v>0</v>
@@ -2597,10 +2597,10 @@
       </c>
       <c r="L39" s="6">
         <f t="shared" si="0"/>
-        <v>10982</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>11113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>97</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>36</v>
       </c>
       <c r="C40" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D40" s="2">
         <v>0</v>
@@ -2636,10 +2636,10 @@
       </c>
       <c r="L40" s="6">
         <f t="shared" si="0"/>
-        <v>98</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>99</v>
       </c>
@@ -2668,60 +2668,60 @@
         <v>0</v>
       </c>
       <c r="J41" s="2">
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="K41" s="2">
         <v>0</v>
       </c>
       <c r="L41" s="6">
         <f t="shared" si="0"/>
-        <v>948</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" customFormat="1" x14ac:dyDescent="0.35">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A42" s="8"/>
       <c r="B42" s="7" t="s">
         <v>47</v>
       </c>
       <c r="C42" s="23">
         <f>SUM(C3:C41)</f>
-        <v>14982875</v>
+        <v>15168928</v>
       </c>
       <c r="D42" s="23">
         <f t="shared" ref="D42:J42" si="1">SUM(D3:D41)</f>
-        <v>1343676</v>
+        <v>1340440</v>
       </c>
       <c r="E42" s="23">
         <f t="shared" si="1"/>
-        <v>27319</v>
+        <v>27413</v>
       </c>
       <c r="F42" s="23">
         <f t="shared" si="1"/>
-        <v>1314</v>
+        <v>1462</v>
       </c>
       <c r="G42" s="23">
         <f t="shared" si="1"/>
-        <v>24595</v>
+        <v>24703</v>
       </c>
       <c r="H42" s="23">
         <f t="shared" si="1"/>
-        <v>435435</v>
+        <v>438279</v>
       </c>
       <c r="I42" s="23">
         <f>SUM(I3:I41)</f>
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J42" s="23">
         <f t="shared" si="1"/>
-        <v>948</v>
+        <v>964</v>
       </c>
       <c r="K42" s="23">
         <f>SUM(K3:K41)</f>
-        <v>2405</v>
+        <v>2426</v>
       </c>
       <c r="L42" s="23">
         <f>SUM(L3:L41)</f>
-        <v>16816203</v>
+        <v>17002233</v>
       </c>
       <c r="M42" s="9"/>
     </row>
@@ -2740,65 +2740,65 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E6AE321-CD75-4C1D-B892-B20887EA78E4}">
   <dimension ref="C1:H31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="54.54296875" customWidth="1"/>
-    <col min="4" max="4" width="24.90625" customWidth="1"/>
+    <col min="3" max="3" width="54.5546875" customWidth="1"/>
+    <col min="4" max="4" width="24.88671875" customWidth="1"/>
     <col min="5" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="16.90625" customWidth="1"/>
+    <col min="7" max="7" width="16.88671875" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C2" s="26" t="s">
+    <row r="1" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C2" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="27"/>
+    </row>
+    <row r="3" spans="3:8" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="28"/>
-    </row>
-    <row r="3" spans="3:8" ht="46.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C3" s="22" t="s">
+      <c r="D3" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="H3" s="29"/>
+    </row>
+    <row r="4" spans="3:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C4" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="H3" s="30"/>
-    </row>
-    <row r="4" spans="3:8" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="C4" s="15" t="s">
+      <c r="D4" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="F4" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="G4" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="H4" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="16" t="s">
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C5" s="17" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C5" s="17" t="s">
-        <v>59</v>
       </c>
       <c r="D5" s="12">
         <v>1949</v>
@@ -2816,9 +2816,9 @@
         <v>2.2575679835813236E-2</v>
       </c>
     </row>
-    <row r="6" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C6" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" s="12">
         <v>158</v>
@@ -2836,9 +2836,9 @@
         <v>5.6962025316455694E-2</v>
       </c>
     </row>
-    <row r="7" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C7" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D7" s="12">
         <v>91220</v>
@@ -2856,9 +2856,9 @@
         <v>5.2291164218373166E-3</v>
       </c>
     </row>
-    <row r="8" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C8" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D8" s="12">
         <v>1559421</v>
@@ -2876,9 +2876,9 @@
         <v>5.2765738052777282E-2</v>
       </c>
     </row>
-    <row r="9" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C9" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D9" s="12">
         <v>12585263</v>
@@ -2896,9 +2896,9 @@
         <v>0.18609019136111815</v>
       </c>
     </row>
-    <row r="10" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C10" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" s="12">
         <v>6925</v>
@@ -2916,9 +2916,9 @@
         <v>1.6750902527075812E-2</v>
       </c>
     </row>
-    <row r="11" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C11" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11" s="12">
         <v>129</v>
@@ -2936,9 +2936,9 @@
         <v>5.4263565891472867E-2</v>
       </c>
     </row>
-    <row r="12" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C12" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12" s="12">
         <v>1162506</v>
@@ -2956,9 +2956,9 @@
         <v>4.7886204458299567E-2</v>
       </c>
     </row>
-    <row r="13" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C13" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D13" s="12">
         <v>9802</v>
@@ -2976,9 +2976,9 @@
         <v>5.1009997959600086E-4</v>
       </c>
     </row>
-    <row r="14" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C14" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" s="12">
         <v>215950</v>
@@ -2996,9 +2996,9 @@
         <v>7.2553831905533689E-2</v>
       </c>
     </row>
-    <row r="15" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C15" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" s="12">
         <v>120062</v>
@@ -3016,9 +3016,9 @@
         <v>8.337359031167231E-3</v>
       </c>
     </row>
-    <row r="16" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C16" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" s="12">
         <v>112769</v>
@@ -3036,9 +3036,9 @@
         <v>8.4881483386391648E-2</v>
       </c>
     </row>
-    <row r="17" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C17" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" s="12">
         <v>4804</v>
@@ -3056,9 +3056,9 @@
         <v>1.6028309741881765E-2</v>
       </c>
     </row>
-    <row r="18" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C18" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D18" s="12">
         <v>94100</v>
@@ -3076,9 +3076,9 @@
         <v>1.1477151965993623E-2</v>
       </c>
     </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C19" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D19" s="12">
         <v>218214</v>
@@ -3096,9 +3096,9 @@
         <v>4.8347035478933523E-3</v>
       </c>
     </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C20" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D20" s="12">
         <v>156658</v>
@@ -3116,7 +3116,7 @@
         <v>8.4904696855570727E-2</v>
       </c>
     </row>
-    <row r="21" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C21" s="24" t="s">
         <v>7</v>
       </c>
@@ -3136,46 +3136,46 @@
         <v>0.15436773596949313</v>
       </c>
     </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
       <c r="C23" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C24" s="14" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C24" s="14" t="s">
+    <row r="25" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C25" s="14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C25" s="14" t="s">
+    <row r="26" spans="3:8" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="30" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="26" spans="3:8" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C26" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="D26" s="32"/>
-    </row>
-    <row r="27" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C27" s="33"/>
-      <c r="D27" s="34"/>
-    </row>
-    <row r="28" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C28" s="33"/>
-      <c r="D28" s="34"/>
-    </row>
-    <row r="29" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C29" s="33"/>
-      <c r="D29" s="34"/>
-    </row>
-    <row r="30" spans="3:8" x14ac:dyDescent="0.35">
-      <c r="C30" s="33"/>
-      <c r="D30" s="34"/>
-    </row>
-    <row r="31" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="C31" s="35"/>
-      <c r="D31" s="36"/>
+      <c r="D26" s="31"/>
+    </row>
+    <row r="27" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C27" s="32"/>
+      <c r="D27" s="33"/>
+    </row>
+    <row r="28" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C28" s="32"/>
+      <c r="D28" s="33"/>
+    </row>
+    <row r="29" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C29" s="32"/>
+      <c r="D29" s="33"/>
+    </row>
+    <row r="30" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="C30" s="32"/>
+      <c r="D30" s="33"/>
+    </row>
+    <row r="31" spans="3:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C31" s="34"/>
+      <c r="D31" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -3186,10 +3186,4 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{a0819fa7-4367-4500-ba88-dd630d977609}" enabled="1" method="Standard" siteId="{63ce7d59-2f3e-42cd-a8cc-be764cff5eb6}" removed="0"/>
-</clbl:labelList>
 </file>